--- a/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
+++ b/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3080,6 +3080,333 @@
       <c r="Z25" s="3" t="inlineStr"/>
       <c r="AA25" s="3" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Ryan Sooklalsingh</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Distribution Manager</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryan-sooklalsingh-19410756/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan Ammon</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonathanammon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>David Franco</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-franco-3a7ba0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
+++ b/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3407,6 +3407,333 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>David Franco</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-franco-3a7ba0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Ryan Sooklalsingh</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Distribution Manager</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ryan-sooklalsingh-19410756/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>A.s. Brydens &amp; Sons (trinidad) Limited</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>San Juan</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>San Juan-Laventille Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Ibis Avenue</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brydenstt.com</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>david.franco@brydenstt.com</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-674-9191</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>118464</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brydens-trinidad-limited/</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brydenshardware/</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/asbryden</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan Ammon</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonathanammon/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
+++ b/BWI/bestwine_output/bestwine_Trinidad and Tobago.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3734,6 +3734,148 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>D'abadie Liquor Mart</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>D'abadie Liquor Mart</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>121134</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>D'Abadie</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Tunapuna/Piarco Regional Corporation</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>5 Eastern Main Road</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>dabadieliquormart@hotmail.com</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063914803236</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dabadieliquor/</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>All Italian Fine Wine And Foods</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>All Italian Fine Wine And Foods</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>117453</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Port of Spain</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Port of Spain Corporation</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>16 O'Connor Street</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>allitaliantt@gmail.com</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+1 868-624-8259</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AllItalianTrinidad/</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/allitaliantt/</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
